--- a/cache基础测试用例清单.xlsx
+++ b/cache基础测试用例清单.xlsx
@@ -661,7 +661,7 @@
           <a:bodyPr/>
           <a:p>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -699,7 +699,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="zh-CN"/>
         </a:p>
@@ -879,7 +879,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="zh-CN"/>
         </a:p>
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K10" s="42" t="inlineStr">
         <is>
-          <t>原始cache.py抛出RuntimeError；cache_fixed.py返回正确KV</t>
+          <t>原始 cache.py 调用 get_kv_pair(0) 时抛出 RuntimeError：The KV for layer:0 have not been set.</t>
         </is>
       </c>
       <c r="L10" s="42" t="inlineStr">
         <is>
-          <t>原始代码不通过，修复版通过</t>
+          <t>不通过</t>
         </is>
       </c>
       <c r="M10" s="42" t="inlineStr">
         <is>
-          <t>pytest</t>
+          <t>缺陷：get_kv_pair 判断条件写反。使用 cache_fixed.py 修复后该用例通过。</t>
         </is>
       </c>
       <c r="N10" s="43" t="n"/>
